--- a/TEST/日報/日報_テスト10.xlsx
+++ b/TEST/日報/日報_テスト10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\日報\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\TEST\日報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D97647E-FCA9-4053-A141-D53A07052E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B238236-0B76-45B2-A06B-BD4229DF1032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="6630" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="10">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -79,27 +79,6 @@
   </si>
   <si>
     <t>NG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>勤怠出勤</t>
-  </si>
-  <si>
-    <t>勤怠退勤</t>
-  </si>
-  <si>
-    <t>禁則チェック</t>
-  </si>
-  <si>
-    <t>禁則あり(特許)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>禁則あり(NG)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>禁則あり(トヨタ)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -107,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,20 +99,6 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -157,13 +122,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -444,13 +405,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A11:K42"/>
+  <dimension ref="A11:D42"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -463,17 +424,8 @@
       <c r="D11" t="s">
         <v>3</v>
       </c>
-      <c r="H11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -486,15 +438,8 @@
       <c r="D12" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11">
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -507,15 +452,8 @@
       <c r="D13" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="4">
-        <v>0.375</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11">
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>3</v>
       </c>
@@ -528,15 +466,8 @@
       <c r="D14" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11">
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>4</v>
       </c>
@@ -549,17 +480,8 @@
       <c r="D15" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>5</v>
       </c>
@@ -572,15 +494,8 @@
       <c r="D16" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11">
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>6</v>
       </c>
@@ -593,15 +508,8 @@
       <c r="D17" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11">
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>7</v>
       </c>
@@ -614,17 +522,8 @@
       <c r="D18" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="4">
-        <v>0.375</v>
-      </c>
-      <c r="I18" s="4">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>8</v>
       </c>
@@ -637,15 +536,8 @@
       <c r="D19" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11">
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>9</v>
       </c>
@@ -658,15 +550,8 @@
       <c r="D20" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11">
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>10</v>
       </c>
@@ -679,15 +564,8 @@
       <c r="D21" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11">
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>11</v>
       </c>
@@ -700,15 +578,8 @@
       <c r="D22" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11">
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>12</v>
       </c>
@@ -721,15 +592,8 @@
       <c r="D23" t="s">
         <v>4</v>
       </c>
-      <c r="H23" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11">
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>13</v>
       </c>
@@ -742,17 +606,8 @@
       <c r="D24" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="4">
-        <v>0.375</v>
-      </c>
-      <c r="I24" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>14</v>
       </c>
@@ -765,15 +620,8 @@
       <c r="D25" t="s">
         <v>4</v>
       </c>
-      <c r="H25" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11">
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>15</v>
       </c>
@@ -786,17 +634,8 @@
       <c r="D26" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>16</v>
       </c>
@@ -809,15 +648,8 @@
       <c r="D27" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11">
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>17</v>
       </c>
@@ -830,15 +662,8 @@
       <c r="D28" t="s">
         <v>4</v>
       </c>
-      <c r="H28" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11">
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>18</v>
       </c>
@@ -851,15 +676,8 @@
       <c r="D29" t="s">
         <v>4</v>
       </c>
-      <c r="H29" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11">
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>19</v>
       </c>
@@ -872,15 +690,8 @@
       <c r="D30" t="s">
         <v>4</v>
       </c>
-      <c r="H30" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I30" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11">
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>20</v>
       </c>
@@ -893,17 +704,8 @@
       <c r="D31" t="s">
         <v>6</v>
       </c>
-      <c r="H31" s="4">
-        <v>0.375</v>
-      </c>
-      <c r="I31" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>21</v>
       </c>
@@ -916,15 +718,8 @@
       <c r="D32" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11">
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>22</v>
       </c>
@@ -937,15 +732,8 @@
       <c r="D33" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11">
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>23</v>
       </c>
@@ -958,15 +746,8 @@
       <c r="D34" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11">
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>24</v>
       </c>
@@ -979,17 +760,8 @@
       <c r="D35" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>25</v>
       </c>
@@ -1002,15 +774,8 @@
       <c r="D36" t="s">
         <v>4</v>
       </c>
-      <c r="H36" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I36" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11">
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>26</v>
       </c>
@@ -1023,15 +788,8 @@
       <c r="D37" t="s">
         <v>4</v>
       </c>
-      <c r="H37" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I37" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11">
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>27</v>
       </c>
@@ -1044,15 +802,8 @@
       <c r="D38" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I38" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11">
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>28</v>
       </c>
@@ -1065,15 +816,8 @@
       <c r="D39" t="s">
         <v>4</v>
       </c>
-      <c r="H39" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11">
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>29</v>
       </c>
@@ -1086,15 +830,8 @@
       <c r="D40" t="s">
         <v>7</v>
       </c>
-      <c r="H40" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I40" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11">
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>30</v>
       </c>
@@ -1107,15 +844,8 @@
       <c r="D41" t="s">
         <v>8</v>
       </c>
-      <c r="H41" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11">
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>31</v>
       </c>
@@ -1128,13 +858,6 @@
       <c r="D42" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="K42" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
